--- a/artfynd/A 26281-2024 artfynd.xlsx
+++ b/artfynd/A 26281-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118420733</v>
+        <v>118420769</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>9367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,20 +1158,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,12 +1179,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1194,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582642</v>
+        <v>582693</v>
       </c>
       <c r="R6" t="n">
-        <v>6426447</v>
+        <v>6426400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,12 +1241,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På vägen</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118420769</v>
+        <v>118420749</v>
       </c>
       <c r="B7" t="n">
-        <v>9367</v>
+        <v>90524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,25 +1283,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101246</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1294,18 +1309,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1313,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582693</v>
+        <v>582698</v>
       </c>
       <c r="R7" t="n">
-        <v>6426400</v>
+        <v>6426525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,11 +1358,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På vägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118420749</v>
+        <v>118420733</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,34 +1401,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1432,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582698</v>
+        <v>582642</v>
       </c>
       <c r="R8" t="n">
-        <v>6426525</v>
+        <v>6426447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1477,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26281-2024 artfynd.xlsx
+++ b/artfynd/A 26281-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118420769</v>
+        <v>118420733</v>
       </c>
       <c r="B6" t="n">
-        <v>9367</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,20 +1158,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101246</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,21 +1179,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1203,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582693</v>
+        <v>582642</v>
       </c>
       <c r="R6" t="n">
-        <v>6426400</v>
+        <v>6426447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1241,18 +1232,12 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På vägen</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118420749</v>
+        <v>118420769</v>
       </c>
       <c r="B7" t="n">
-        <v>90524</v>
+        <v>9367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,25 +1268,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>101246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1309,12 +1294,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582698</v>
+        <v>582693</v>
       </c>
       <c r="R7" t="n">
-        <v>6426525</v>
+        <v>6426400</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,6 +1349,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På vägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118420733</v>
+        <v>118420749</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>90531</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,31 +1397,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1433,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582642</v>
+        <v>582698</v>
       </c>
       <c r="R8" t="n">
-        <v>6426447</v>
+        <v>6426525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,6 +1476,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>118442043</v>
       </c>
       <c r="B9" t="n">
-        <v>109751</v>
+        <v>109758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>118488199</v>
       </c>
       <c r="B10" t="n">
-        <v>90488</v>
+        <v>90495</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 26281-2024 artfynd.xlsx
+++ b/artfynd/A 26281-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118420733</v>
+        <v>118420749</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>90531</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582642</v>
+        <v>582698</v>
       </c>
       <c r="R6" t="n">
-        <v>6426447</v>
+        <v>6426525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1381,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118420749</v>
+        <v>118420733</v>
       </c>
       <c r="B8" t="n">
-        <v>90531</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,34 +1401,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1432,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582698</v>
+        <v>582642</v>
       </c>
       <c r="R8" t="n">
-        <v>6426525</v>
+        <v>6426447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1477,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
